--- a/03_Outputs/Bioenergetica_Norte/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/03_Ordenamiento/ordenamiento.xlsx
@@ -148,7 +148,7 @@
     <numFmt numFmtId="272" formatCode="#,##0.0"/>
     <numFmt numFmtId="273" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,23 +158,335 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -194,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -203,111 +515,167 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="176" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="178" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="240" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="246" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="252" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="253" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="254" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="254" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="255" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="256" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="256" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="257" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="258" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="258" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="259" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="260" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="260" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="261" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="263" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="16" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="265" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="266" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="266" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="267" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="268" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="268" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="269" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="270" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="270" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="271" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="19" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="273" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="17" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="18" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="19" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="20" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="21" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="22" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="23" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="24" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="25" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="34" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="26" fontId="34" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,12 +1004,12 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="101.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="102.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1110,35 +1478,35 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="137" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="137" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="137" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="137" t="inlineStr">
         <is>
           <t>Predios con uso adecuado del suelo rural</t>
         </is>
@@ -1163,7 +1531,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="112">
+      <c r="E2" s="138">
         <v>0.15097869566661</v>
       </c>
     </row>
@@ -1186,7 +1554,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="112">
+      <c r="E3" s="138">
         <v>0.534574496012986</v>
       </c>
     </row>
@@ -1209,7 +1577,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="112">
+      <c r="E4" s="138">
         <v>0.270116020859396</v>
       </c>
     </row>
@@ -1232,7 +1600,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="112">
+      <c r="E5" s="138">
         <v>0.180285116103234</v>
       </c>
     </row>
@@ -1255,7 +1623,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="112">
+      <c r="E6" s="138">
         <v>0.340186905218954</v>
       </c>
     </row>
@@ -1278,7 +1646,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="112">
+      <c r="E7" s="138">
         <v>0.300109988211582</v>
       </c>
     </row>
@@ -1301,7 +1669,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="112">
+      <c r="E8" s="138">
         <v>0.143171126425268</v>
       </c>
     </row>
@@ -1324,7 +1692,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="112">
+      <c r="E9" s="138">
         <v>0.53383102720126</v>
       </c>
     </row>
@@ -1347,7 +1715,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="112">
+      <c r="E10" s="138">
         <v>0.288747802724</v>
       </c>
     </row>
@@ -1370,7 +1738,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="112">
+      <c r="E11" s="138">
         <v>0.258658277306015</v>
       </c>
     </row>
@@ -1393,7 +1761,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="112">
+      <c r="E12" s="138">
         <v>0.253411364838396</v>
       </c>
     </row>
@@ -1416,7 +1784,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="112">
+      <c r="E13" s="138">
         <v>0.295177446596649</v>
       </c>
     </row>
@@ -1439,7 +1807,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="112">
+      <c r="E14" s="138">
         <v>0.255039730029715</v>
       </c>
     </row>
@@ -1455,17 +1823,17 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="140" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="140" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1613,17 +1981,17 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="142" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1771,23 +2139,22 @@
   <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="144" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="144" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2390,23 +2757,23 @@
   <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="146" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="146" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="146" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3009,17 +3376,17 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="148" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3167,17 +3534,17 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="150" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3325,23 +3692,23 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="152" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="152" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="152" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3539,23 +3906,23 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="154" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="154" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="154" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3903,17 +4270,17 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="156" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="156" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -4061,101 +4428,101 @@
   <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="84.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="85.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (municipal)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (agregado)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (municipal)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (agregado)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (municipal)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (agregado)</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (municipal)</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (agregado)</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (municipal)</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (agregado)</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (municipal)</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (agregado)</t>
         </is>
@@ -4180,50 +4547,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>0.997846859162327</v>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G2" s="12">
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" s="15">
         <v>0.866726415187737</v>
       </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" s="16">
+      <c r="H2" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" s="19">
         <v>0.385272538075969</v>
       </c>
-      <c r="J2" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" s="20">
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" s="23">
         <v>0.471281778360012</v>
       </c>
-      <c r="L2" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" s="24">
+      <c r="L2" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" s="27">
         <v>0.260320533557237</v>
       </c>
-      <c r="N2" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" s="28">
+      <c r="N2" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" s="31">
         <v>0.312065749595099</v>
       </c>
-      <c r="P2" s="30" t="inlineStr">
+      <c r="P2" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4248,50 +4615,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>0.982530645827883</v>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" s="12">
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" s="15">
         <v>0.777187010643098</v>
       </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" s="16">
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" s="19">
         <v>0.597006605014806</v>
       </c>
-      <c r="J3" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" s="20">
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" s="23">
         <v>0.93897290503111</v>
       </c>
-      <c r="L3" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" s="24">
+      <c r="L3" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" s="27">
         <v>0.372574590788621</v>
       </c>
-      <c r="N3" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" s="28">
+      <c r="N3" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" s="31">
         <v>0.467804723609326</v>
       </c>
-      <c r="P3" s="30" t="inlineStr">
+      <c r="P3" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4316,50 +4683,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>0.979954996622595</v>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G4" s="12">
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" s="15">
         <v>0.668601324286766</v>
       </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" s="16">
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" s="19">
         <v>0.550392166142488</v>
       </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" s="20">
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" s="23">
         <v>0.757773408425011</v>
       </c>
-      <c r="L4" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" s="24">
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" s="27">
         <v>0.261707977128303</v>
       </c>
-      <c r="N4" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" s="28">
+      <c r="N4" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" s="31">
         <v>0</v>
       </c>
-      <c r="P4" s="30" t="inlineStr">
+      <c r="P4" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4384,50 +4751,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="11">
         <v>0.98190433351282</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" s="12">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" s="15">
         <v>0.825160553169694</v>
       </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" s="16">
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" s="19">
         <v>0.403098993560363</v>
       </c>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" s="20">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" s="23">
         <v>0.414143234878234</v>
       </c>
-      <c r="L5" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" s="24">
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" s="27">
         <v>0.288618892522403</v>
       </c>
-      <c r="N5" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" s="28">
+      <c r="N5" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" s="31">
         <v>0.344563190312964</v>
       </c>
-      <c r="P5" s="30" t="inlineStr">
+      <c r="P5" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4452,50 +4819,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>0.996840747904578</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" s="12">
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" s="15">
         <v>0.961534493874919</v>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" s="16">
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" s="19">
         <v>0.911540941328175</v>
       </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" s="20">
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" s="23">
         <v>0.977330754352031</v>
       </c>
-      <c r="L6" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" s="24">
+      <c r="L6" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" s="27">
         <v>0.43886524822695</v>
       </c>
-      <c r="N6" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" s="28">
+      <c r="N6" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" s="31">
         <v>0.785944551901999</v>
       </c>
-      <c r="P6" s="30" t="inlineStr">
+      <c r="P6" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4520,50 +4887,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>0.986584446194474</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" s="12">
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" s="15">
         <v>0.959663178047579</v>
       </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I7" s="16">
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" s="19">
         <v>0.821035788723811</v>
       </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K7" s="20">
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" s="23">
         <v>0.928360219168019</v>
       </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M7" s="24">
+      <c r="L7" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" s="27">
         <v>0.353222265199981</v>
       </c>
-      <c r="N7" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O7" s="28">
+      <c r="N7" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" s="31">
         <v>0.640899490481663</v>
       </c>
-      <c r="P7" s="30" t="inlineStr">
+      <c r="P7" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4588,50 +4955,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="11">
         <v>0.986953086419753</v>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" s="12">
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" s="15">
         <v>0.774761728395062</v>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I8" s="16">
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" s="19">
         <v>0.523429629629629</v>
       </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K8" s="20">
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" s="23">
         <v>0.973548148148148</v>
       </c>
-      <c r="L8" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M8" s="24">
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" s="27">
         <v>0.269530864197531</v>
       </c>
-      <c r="N8" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O8" s="28">
+      <c r="N8" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" s="31">
         <v>0.407658024691358</v>
       </c>
-      <c r="P8" s="30" t="inlineStr">
+      <c r="P8" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4656,50 +5023,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="11">
         <v>1</v>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" s="12">
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" s="15">
         <v>1</v>
       </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I9" s="16">
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" s="19">
         <v>0.881931408415767</v>
       </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K9" s="20">
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" s="23">
         <v>0.960551930280487</v>
       </c>
-      <c r="L9" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M9" s="24">
+      <c r="L9" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" s="27">
         <v>0.121966034395524</v>
       </c>
-      <c r="N9" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O9" s="28">
+      <c r="N9" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" s="31">
         <v>0.704828521039417</v>
       </c>
-      <c r="P9" s="30" t="inlineStr">
+      <c r="P9" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4724,50 +5091,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="11">
         <v>0.994674159731979</v>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" s="12">
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" s="15">
         <v>0.709544336971793</v>
       </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I10" s="16">
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" s="19">
         <v>0.488946828055765</v>
       </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K10" s="20">
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" s="23">
         <v>0.75385050794337</v>
       </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M10" s="24">
+      <c r="L10" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" s="27">
         <v>0.247561196368745</v>
       </c>
-      <c r="N10" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O10" s="28">
+      <c r="N10" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" s="31">
         <v>0.432289527720739</v>
       </c>
-      <c r="P10" s="30" t="inlineStr">
+      <c r="P10" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4792,50 +5159,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="11">
         <v>1</v>
       </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" s="12">
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" s="15">
         <v>0.885304912478825</v>
       </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I11" s="16">
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" s="19">
         <v>0.680872716767559</v>
       </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K11" s="20">
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" s="23">
         <v>0.934990249891665</v>
       </c>
-      <c r="L11" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M11" s="24">
+      <c r="L11" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" s="27">
         <v>0.269910574763962</v>
       </c>
-      <c r="N11" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O11" s="28">
+      <c r="N11" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" s="31">
         <v>0.672630264073641</v>
       </c>
-      <c r="P11" s="30" t="inlineStr">
+      <c r="P11" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4860,50 +5227,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="11">
         <v>0.984875204290455</v>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" s="12">
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" s="15">
         <v>0.950299840372751</v>
       </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I12" s="16">
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" s="19">
         <v>0.69073928826666</v>
       </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K12" s="20">
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" s="23">
         <v>0.642112867746265</v>
       </c>
-      <c r="L12" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M12" s="24">
+      <c r="L12" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" s="27">
         <v>0.134466328618832</v>
       </c>
-      <c r="N12" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O12" s="28">
+      <c r="N12" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" s="31">
         <v>0.510346294930166</v>
       </c>
-      <c r="P12" s="30" t="inlineStr">
+      <c r="P12" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4928,50 +5295,50 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="11">
         <v>0.990125260474267</v>
       </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" s="12">
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" s="15">
         <v>0.891590319088253</v>
       </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I13" s="16">
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" s="19">
         <v>0.654809024341975</v>
       </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K13" s="20">
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" s="23">
         <v>0.996779238115194</v>
       </c>
-      <c r="L13" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M13" s="24">
+      <c r="L13" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" s="27">
         <v>0.257202089226746</v>
       </c>
-      <c r="N13" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O13" s="28">
+      <c r="N13" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" s="31">
         <v>0.284276861348141</v>
       </c>
-      <c r="P13" s="30" t="inlineStr">
+      <c r="P13" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4996,262 +5363,262 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="11">
         <v>1</v>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" s="12">
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" s="15">
         <v>0.930451871938449</v>
       </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I14" s="16">
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" s="19">
         <v>0.851315408859874</v>
       </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K14" s="20">
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" s="23">
         <v>0.895421749938183</v>
       </c>
-      <c r="L14" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M14" s="24">
+      <c r="L14" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" s="27">
         <v>0.54021667976634</v>
       </c>
-      <c r="N14" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O14" s="28">
+      <c r="N14" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" s="31">
         <v>0.755933103557518</v>
       </c>
-      <c r="P14" s="30" t="inlineStr">
+      <c r="P14" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA (promedio ponderado; sin ECV oficial)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F15" s="11">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" s="14">
         <v>0.993049509714873</v>
       </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H15" s="15">
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H15" s="18">
         <v>0.884982678254471</v>
       </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J15" s="19">
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" s="22">
         <v>0.702731807269917</v>
       </c>
-      <c r="K15" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L15" s="23">
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" s="26">
         <v>0.851174798025616</v>
       </c>
-      <c r="M15" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N15" s="27">
+      <c r="M15" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" s="30">
         <v>0.328072501657953</v>
       </c>
-      <c r="O15" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P15" s="31">
+      <c r="O15" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" s="34">
         <v>0.543381396070275</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>SUBREGIÓN NORTE (ECV oficial)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F16" s="11">
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F16" s="14">
         <v>0.995995299069986</v>
       </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H16" s="15">
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H16" s="18">
         <v>0.893102677644782</v>
       </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J16" s="19">
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" s="22">
         <v>0.728573914060344</v>
       </c>
-      <c r="K16" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L16" s="23">
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" s="26">
         <v>0.884143853052556</v>
       </c>
-      <c r="M16" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N16" s="27">
+      <c r="M16" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" s="30">
         <v>0.401126509950594</v>
       </c>
-      <c r="O16" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P16" s="31">
+      <c r="O16" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" s="34">
         <v>0.562700217903468</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>DEPARTAMENTO (ANTIOQUIA) (ECV oficial)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F17" s="11">
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" s="14">
         <v>0.992586544500931</v>
       </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H17" s="15">
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H17" s="18">
         <v>0.93579635079431</v>
       </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J17" s="19">
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" s="22">
         <v>0.866893560801633</v>
       </c>
-      <c r="K17" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L17" s="23">
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" s="26">
         <v>0.944698426552535</v>
       </c>
-      <c r="M17" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N17" s="27">
+      <c r="M17" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N17" s="30">
         <v>0.601239746666835</v>
       </c>
-      <c r="O17" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P17" s="31">
+      <c r="O17" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" s="34">
         <v>0.66955125810138</v>
       </c>
     </row>
@@ -5267,17 +5634,17 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="158" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="158" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5415,17 +5782,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="160" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5553,17 +5920,17 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="162" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="162" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5711,17 +6078,17 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="164" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="164" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5734,7 +6101,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>109.103988490129</v>
+        <v>45.7996962672848</v>
       </c>
     </row>
     <row r="3">
@@ -5744,7 +6111,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>464.939386736392</v>
+        <v>135.393391965771</v>
       </c>
     </row>
     <row r="4">
@@ -5754,7 +6121,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>313.183360563026</v>
+        <v>79.5525951991957</v>
       </c>
     </row>
     <row r="5">
@@ -5764,7 +6131,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>218.890554722639</v>
+        <v>78.5607196401799</v>
       </c>
     </row>
     <row r="6">
@@ -5774,7 +6141,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>564.94165398275</v>
+        <v>140.284119736175</v>
       </c>
     </row>
     <row r="7">
@@ -5784,7 +6151,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>470.644943603586</v>
+        <v>111.925190398149</v>
       </c>
     </row>
     <row r="8">
@@ -5794,7 +6161,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>204.023398487659</v>
+        <v>72.7635896704237</v>
       </c>
     </row>
     <row r="9">
@@ -5804,7 +6171,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>61.324750127054</v>
+        <v>18.5329493477893</v>
       </c>
     </row>
     <row r="10">
@@ -5814,7 +6181,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>213.455822750608</v>
+        <v>56.8765198594974</v>
       </c>
     </row>
     <row r="11">
@@ -5824,7 +6191,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>158.576051779935</v>
+        <v>23.898431665422</v>
       </c>
     </row>
     <row r="12">
@@ -5834,7 +6201,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>121.268656716418</v>
+        <v>38.1426202321725</v>
       </c>
     </row>
     <row r="13">
@@ -5844,7 +6211,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>231.650459571067</v>
+        <v>62.2752098041828</v>
       </c>
     </row>
     <row r="14">
@@ -5854,7 +6221,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>432.145926845574</v>
+        <v>130.121287365104</v>
       </c>
     </row>
   </sheetData>
@@ -5869,17 +6236,17 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="166" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="166" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5892,7 +6259,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.338461538461538</v>
+        <v>0.556719022687609</v>
       </c>
     </row>
     <row r="3">
@@ -5902,7 +6269,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.645705521472393</v>
+        <v>0.640800561797753</v>
       </c>
     </row>
     <row r="4">
@@ -5912,7 +6279,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.0208667736757624</v>
+        <v>0.0221169036334913</v>
       </c>
     </row>
     <row r="5">
@@ -5922,7 +6289,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.784931506849315</v>
+        <v>0.783715012722646</v>
       </c>
     </row>
     <row r="6">
@@ -5932,7 +6299,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.871576111360575</v>
+        <v>0.793851717902351</v>
       </c>
     </row>
     <row r="7">
@@ -5942,7 +6309,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.870544858664482</v>
+        <v>0.787252368647718</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +6319,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.505594405594406</v>
+        <v>0.543137254901961</v>
       </c>
     </row>
     <row r="9">
@@ -5962,7 +6329,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.0812154696132597</v>
+        <v>0.00731261425959781</v>
       </c>
     </row>
     <row r="10">
@@ -5972,7 +6339,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.836708860759494</v>
+        <v>0.783847980997625</v>
       </c>
     </row>
     <row r="11">
@@ -5982,7 +6349,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.601255886970173</v>
+        <v>0.0208333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -5992,7 +6359,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.172649572649573</v>
+        <v>0.0108695652173913</v>
       </c>
     </row>
     <row r="13">
@@ -6002,7 +6369,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.205577918343876</v>
+        <v>0.300534759358289</v>
       </c>
     </row>
     <row r="14">
@@ -6012,7 +6379,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.872044198895028</v>
+        <v>0.877064220183486</v>
       </c>
     </row>
   </sheetData>
@@ -6027,29 +6394,29 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="168" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="168" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="168" t="inlineStr">
         <is>
           <t>Déficit cuantitativo de vivienda</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="168" t="inlineStr">
         <is>
           <t>Déficit cualitativo de vivienda</t>
         </is>
@@ -6275,47 +6642,47 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="90.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="91.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="36" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="36" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="36" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="36" t="inlineStr">
         <is>
           <t>Km de vía primaria por km² del municipio</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="36" t="inlineStr">
         <is>
           <t>Km de vía secundaria por km² del municipio</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="36" t="inlineStr">
         <is>
           <t>Km de vía terciaria por km² del municipio</t>
         </is>
@@ -6340,13 +6707,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="38">
         <v>0.0400873284500982</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="40">
         <v>0.0670298158898514</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="42">
         <v>0.289606040359022</v>
       </c>
     </row>
@@ -6369,13 +6736,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="38">
         <v>0</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="40">
         <v>0.0405995375622717</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="42">
         <v>0.212486288968215</v>
       </c>
     </row>
@@ -6398,13 +6765,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="38">
         <v>0</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="40">
         <v>0.0946641234143567</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="42">
         <v>0.487476572417853</v>
       </c>
     </row>
@@ -6427,13 +6794,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="38">
         <v>0</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="40">
         <v>0.119733832902162</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="42">
         <v>0.429444309699584</v>
       </c>
     </row>
@@ -6456,13 +6823,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="38">
         <v>0</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="40">
         <v>0.306258340884817</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="42">
         <v>0.153254866182126</v>
       </c>
     </row>
@@ -6485,13 +6852,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="38">
         <v>0</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="40">
         <v>0.122566188369185</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="42">
         <v>0.242911837355881</v>
       </c>
     </row>
@@ -6514,13 +6881,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="38">
         <v>0</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="40">
         <v>0.0958192093473051</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="42">
         <v>0.517798013682005</v>
       </c>
     </row>
@@ -6543,13 +6910,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="38">
         <v>0</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="40">
         <v>0.012025770411889</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="42">
         <v>0.0657740356514282</v>
       </c>
     </row>
@@ -6572,13 +6939,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="38">
         <v>0</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="40">
         <v>0.291686833371828</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="42">
         <v>0.327176295770876</v>
       </c>
     </row>
@@ -6601,13 +6968,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="38">
         <v>0</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="40">
         <v>0.27816414694807</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="42">
         <v>0.338268866671721</v>
       </c>
     </row>
@@ -6630,13 +6997,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="38">
         <v>0</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="40">
         <v>0.311779097203111</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="42">
         <v>0.364249551472128</v>
       </c>
     </row>
@@ -6659,13 +7026,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="38">
         <v>0.0961138784482969</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="40">
         <v>0.0112761616798996</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="42">
         <v>0.192872918896798</v>
       </c>
     </row>
@@ -6688,44 +7055,44 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="38">
         <v>0.0544834167608284</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="40">
         <v>0.0388717924309366</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="42">
         <v>0.472611391127601</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA (por área del municipio)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="33">
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="39">
         <v>0.0143535230532359</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="41">
         <v>0.0588957188561701</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="43">
         <v>0.217167305948679</v>
       </c>
     </row>
@@ -6741,47 +7108,47 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="81.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="82.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Km de vía primaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Km de vía secundaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Km de vía terciaria por cada 1.000 hab.</t>
         </is>
@@ -6806,13 +7173,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="47">
         <v>1.13033338953416</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="49">
         <v>1.89002465177849</v>
       </c>
-      <c r="G2" s="42">
+      <c r="G2" s="51">
         <v>8.16595642276528</v>
       </c>
     </row>
@@ -6835,13 +7202,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="47">
         <v>0</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="49">
         <v>2.93945001282605</v>
       </c>
-      <c r="G3" s="42">
+      <c r="G3" s="51">
         <v>15.384234952799</v>
       </c>
     </row>
@@ -6864,13 +7231,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="47">
         <v>0</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="49">
         <v>4.20471329391572</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="51">
         <v>21.6523340690118</v>
       </c>
     </row>
@@ -6893,13 +7260,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="47">
         <v>0</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="49">
         <v>2.87469860984191</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="51">
         <v>10.310560767788</v>
       </c>
     </row>
@@ -6922,13 +7289,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="47">
         <v>0</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="49">
         <v>10.9751732624012</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="51">
         <v>5.49209110450821</v>
       </c>
     </row>
@@ -6951,13 +7318,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="47">
         <v>0</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="49">
         <v>3.95311214225888</v>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="51">
         <v>7.83460550194749</v>
       </c>
     </row>
@@ -6980,13 +7347,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="47">
         <v>0</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="49">
         <v>1.63537261436958</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="51">
         <v>8.83740011129964</v>
       </c>
     </row>
@@ -7009,13 +7376,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="47">
         <v>0</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="49">
         <v>1.19321819476477</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="51">
         <v>6.52621606718858</v>
       </c>
     </row>
@@ -7038,13 +7405,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="47">
         <v>0</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="49">
         <v>7.94143813805682</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="51">
         <v>8.9076708847906</v>
       </c>
     </row>
@@ -7067,13 +7434,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="47">
         <v>0</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="49">
         <v>9.06882618526614</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="51">
         <v>11.0283858987244</v>
       </c>
     </row>
@@ -7096,13 +7463,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="47">
         <v>0</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="49">
         <v>8.02227595424822</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="51">
         <v>9.37237436484369</v>
       </c>
     </row>
@@ -7125,13 +7492,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="47">
         <v>3.73829145703461</v>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="49">
         <v>0.438579522090407</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="51">
         <v>7.5016761017826</v>
       </c>
     </row>
@@ -7154,44 +7521,44 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="47">
         <v>0.880308359058089</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="49">
         <v>0.628065672876939</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="51">
         <v>7.63615395161522</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA (por población)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="39">
+      <c r="C15" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="48">
         <v>0.610945328703975</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="50">
         <v>2.55270035072234</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="52">
         <v>9.35922803198561</v>
       </c>
     </row>
@@ -7207,71 +7574,71 @@
   <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="54" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral total ($)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral urbano ($)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral rural ($)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral urbano sobre el total</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral rural sobre el total</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro rural</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro urbano</t>
         </is>
@@ -7296,19 +7663,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="56">
         <v>246991880000</v>
       </c>
-      <c r="F2" s="46">
+      <c r="F2" s="58">
         <v>77202765000</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="60">
         <v>169789115000</v>
       </c>
-      <c r="H2" s="50">
+      <c r="H2" s="62">
         <v>0.312572077268289</v>
       </c>
-      <c r="I2" s="52">
+      <c r="I2" s="64">
         <v>0.687427922731711</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -7341,19 +7708,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="56">
         <v>413207754000</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="58">
         <v>129212280000</v>
       </c>
-      <c r="G3" s="48">
+      <c r="G3" s="60">
         <v>283995474000</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="62">
         <v>0.312705361284193</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3" s="64">
         <v>0.687294638715807</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -7386,19 +7753,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="56">
         <v>86337310000</v>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="58">
         <v>29711783000</v>
       </c>
-      <c r="G4" s="48">
+      <c r="G4" s="60">
         <v>56625527000</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="62">
         <v>0.3441360751221</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4" s="64">
         <v>0.6558639248779</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -7431,19 +7798,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="56">
         <v>127040220000</v>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="58">
         <v>41468302000</v>
       </c>
-      <c r="G5" s="48">
+      <c r="G5" s="60">
         <v>85571918000</v>
       </c>
-      <c r="H5" s="50">
+      <c r="H5" s="62">
         <v>0.326418688506679</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="64">
         <v>0.673581311493321</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -7476,19 +7843,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="56">
         <v>301213251023</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="58">
         <v>192072956023</v>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="60">
         <v>109140295000</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="62">
         <v>0.637664363605085</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="64">
         <v>0.362335636394915</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -7521,19 +7888,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="56">
         <v>540115348000</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="58">
         <v>229615240000</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="60">
         <v>310500108000</v>
       </c>
-      <c r="H7" s="50">
+      <c r="H7" s="62">
         <v>0.425122598071403</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="64">
         <v>0.574877401928597</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -7566,19 +7933,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="56">
         <v>202816396000</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="58">
         <v>52167955000</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="60">
         <v>150648441000</v>
       </c>
-      <c r="H8" s="50">
+      <c r="H8" s="62">
         <v>0.257217641319295</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8" s="64">
         <v>0.742782358680706</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -7611,19 +7978,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="56">
         <v>508471421000</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="58">
         <v>137407431000</v>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="60">
         <v>371063990000</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="62">
         <v>0.270236291215274</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="64">
         <v>0.729763708784726</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -7656,19 +8023,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="56">
         <v>135539116000</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="58">
         <v>65124212000</v>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="60">
         <v>70414904000</v>
       </c>
-      <c r="H10" s="50">
+      <c r="H10" s="62">
         <v>0.480482785500829</v>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="64">
         <v>0.519517214499171</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -7701,19 +8068,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="56">
         <v>109634106000</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="58">
         <v>64717982000</v>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="60">
         <v>44916124000</v>
       </c>
-      <c r="H11" s="50">
+      <c r="H11" s="62">
         <v>0.590308840571929</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11" s="64">
         <v>0.409691159428071</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -7746,19 +8113,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="56">
         <v>90454486000</v>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="58">
         <v>53924844000</v>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="60">
         <v>36529642000</v>
       </c>
-      <c r="H12" s="50">
+      <c r="H12" s="62">
         <v>0.596154446115586</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12" s="64">
         <v>0.403845553884414</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -7791,19 +8158,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="44">
+      <c r="E13" s="56">
         <v>122792806000</v>
       </c>
-      <c r="F13" s="46">
+      <c r="F13" s="58">
         <v>57749002000</v>
       </c>
-      <c r="G13" s="48">
+      <c r="G13" s="60">
         <v>65043804000</v>
       </c>
-      <c r="H13" s="50">
+      <c r="H13" s="62">
         <v>0.470296297325431</v>
       </c>
-      <c r="I13" s="52">
+      <c r="I13" s="64">
         <v>0.529703702674569</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -7836,19 +8203,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="56">
         <v>1977484809248</v>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="58">
         <v>1348173138033</v>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="60">
         <v>629311671215</v>
       </c>
-      <c r="H14" s="50">
+      <c r="H14" s="62">
         <v>0.681761564856564</v>
       </c>
-      <c r="I14" s="52">
+      <c r="I14" s="64">
         <v>0.318238435143436</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -7863,47 +8230,47 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="45">
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="57">
         <v>4862098903271</v>
       </c>
-      <c r="F15" s="47">
+      <c r="F15" s="59">
         <v>2478547890056</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="61">
         <v>2383551013215</v>
       </c>
-      <c r="H15" s="51">
+      <c r="H15" s="63">
         <v>0.50976912221768</v>
       </c>
-      <c r="I15" s="53">
+      <c r="I15" s="65">
         <v>0.49023087778232</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="J15" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7921,100 +8288,100 @@
   <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="86.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="87.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="67" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="67" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="67" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="67" t="inlineStr">
         <is>
           <t>IMCA total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="67" t="inlineStr">
         <is>
           <t>IMCA adopción TIC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="67" t="inlineStr">
         <is>
           <t>IMCA capacidades</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="67" t="inlineStr">
         <is>
           <t>IMCA dinamismo de los negocios</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="67" t="inlineStr">
         <is>
           <t>IMCA infraestructura</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="67" t="inlineStr">
         <is>
           <t>IMCA innovación</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="67" t="inlineStr">
         <is>
           <t>IMCA instituciones</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado de bienes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado laboral</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="67" t="inlineStr">
         <is>
           <t>IMCA salud</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="67" t="inlineStr">
         <is>
           <t>IMCA sistema financiero</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="67" t="inlineStr">
         <is>
           <t>IMCA tamaño del mercado</t>
         </is>
@@ -8039,40 +8406,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="54">
+      <c r="E2" s="69">
         <v>30.1608606631865</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="71">
         <v>4.26941478587025</v>
       </c>
-      <c r="G2" s="58">
+      <c r="G2" s="73">
         <v>28.8040327958118</v>
       </c>
-      <c r="H2" s="60">
+      <c r="H2" s="75">
         <v>60.1431637865114</v>
       </c>
-      <c r="I2" s="62">
+      <c r="I2" s="77">
         <v>43.7027064994041</v>
       </c>
-      <c r="J2" s="64">
+      <c r="J2" s="79">
         <v>0</v>
       </c>
-      <c r="K2" s="66">
+      <c r="K2" s="81">
         <v>51.1861734414198</v>
       </c>
-      <c r="L2" s="68">
+      <c r="L2" s="83">
         <v>2.90124942793754</v>
       </c>
-      <c r="M2" s="70">
+      <c r="M2" s="85">
         <v>58.2301524460056</v>
       </c>
-      <c r="N2" s="72">
+      <c r="N2" s="87">
         <v>45.6120827511501</v>
       </c>
-      <c r="O2" s="74">
+      <c r="O2" s="89">
         <v>18.0219387737386</v>
       </c>
-      <c r="P2" s="76">
+      <c r="P2" s="91">
         <v>18.8985525872026</v>
       </c>
     </row>
@@ -8095,40 +8462,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="54">
+      <c r="E3" s="69">
         <v>28.1564781000416</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="71">
         <v>5.91434732958735</v>
       </c>
-      <c r="G3" s="58">
+      <c r="G3" s="73">
         <v>32.6638002337587</v>
       </c>
-      <c r="H3" s="60">
+      <c r="H3" s="75">
         <v>51.8125567672495</v>
       </c>
-      <c r="I3" s="62">
+      <c r="I3" s="77">
         <v>47.5525535601599</v>
       </c>
-      <c r="J3" s="64">
+      <c r="J3" s="79">
         <v>0</v>
       </c>
-      <c r="K3" s="66">
+      <c r="K3" s="81">
         <v>45.0630492381031</v>
       </c>
-      <c r="L3" s="68">
+      <c r="L3" s="83">
         <v>12.6557158276985</v>
       </c>
-      <c r="M3" s="70">
+      <c r="M3" s="85">
         <v>42.0479569364456</v>
       </c>
-      <c r="N3" s="72">
+      <c r="N3" s="87">
         <v>42.6011542351243</v>
       </c>
-      <c r="O3" s="74">
+      <c r="O3" s="89">
         <v>16.8883670652238</v>
       </c>
-      <c r="P3" s="76">
+      <c r="P3" s="91">
         <v>12.5217579071074</v>
       </c>
     </row>
@@ -8151,40 +8518,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="69">
         <v>26.313756869038</v>
       </c>
-      <c r="F4" s="56">
+      <c r="F4" s="71">
         <v>6.18675588738366</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4" s="73">
         <v>26.1070752847623</v>
       </c>
-      <c r="H4" s="60">
+      <c r="H4" s="75">
         <v>31.5472401943649</v>
       </c>
-      <c r="I4" s="62">
+      <c r="I4" s="77">
         <v>45.096422398983</v>
       </c>
-      <c r="J4" s="64">
+      <c r="J4" s="79">
         <v>0</v>
       </c>
-      <c r="K4" s="66">
+      <c r="K4" s="81">
         <v>49.0757932152676</v>
       </c>
-      <c r="L4" s="68">
+      <c r="L4" s="83">
         <v>2.18542475760491</v>
       </c>
-      <c r="M4" s="70">
+      <c r="M4" s="85">
         <v>50.8293021393744</v>
       </c>
-      <c r="N4" s="72">
+      <c r="N4" s="87">
         <v>53.3454057081201</v>
       </c>
-      <c r="O4" s="74">
+      <c r="O4" s="89">
         <v>11.5226040208981</v>
       </c>
-      <c r="P4" s="76">
+      <c r="P4" s="91">
         <v>13.5553019526585</v>
       </c>
     </row>
@@ -8207,40 +8574,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="69">
         <v>27.6737614748969</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="71">
         <v>3.14838447914831</v>
       </c>
-      <c r="G5" s="58">
+      <c r="G5" s="73">
         <v>27.3163474164098</v>
       </c>
-      <c r="H5" s="60">
+      <c r="H5" s="75">
         <v>57.8263862171158</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="77">
         <v>48.6061063072135</v>
       </c>
-      <c r="J5" s="64">
+      <c r="J5" s="79">
         <v>0</v>
       </c>
-      <c r="K5" s="66">
+      <c r="K5" s="81">
         <v>48.0943893515983</v>
       </c>
-      <c r="L5" s="68">
+      <c r="L5" s="83">
         <v>0.774511007430114</v>
       </c>
-      <c r="M5" s="70">
+      <c r="M5" s="85">
         <v>41.3687174867793</v>
       </c>
-      <c r="N5" s="72">
+      <c r="N5" s="87">
         <v>40.096825719688</v>
       </c>
-      <c r="O5" s="74">
+      <c r="O5" s="89">
         <v>22.7757463346955</v>
       </c>
-      <c r="P5" s="76">
+      <c r="P5" s="91">
         <v>14.4039619037879</v>
       </c>
     </row>
@@ -8263,40 +8630,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="69">
         <v>35.6100246449063</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="71">
         <v>7.97953790090281</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="73">
         <v>55.0420659315978</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="75">
         <v>59.6011163850901</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="77">
         <v>55.3916562515055</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="79">
         <v>0</v>
       </c>
-      <c r="K6" s="66">
+      <c r="K6" s="81">
         <v>61.6512457303834</v>
       </c>
-      <c r="L6" s="68">
+      <c r="L6" s="83">
         <v>7.61456421485926</v>
       </c>
-      <c r="M6" s="70">
+      <c r="M6" s="85">
         <v>47.915355206486</v>
       </c>
-      <c r="N6" s="72">
+      <c r="N6" s="87">
         <v>48.6048123203123</v>
       </c>
-      <c r="O6" s="74">
+      <c r="O6" s="89">
         <v>21.3695946618205</v>
       </c>
-      <c r="P6" s="76">
+      <c r="P6" s="91">
         <v>26.5403224910112</v>
       </c>
     </row>
@@ -8319,40 +8686,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="54">
+      <c r="E7" s="69">
         <v>32.2136105609074</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="71">
         <v>7.31763720020136</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="73">
         <v>38.7534946881358</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="75">
         <v>64.157505868347</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="77">
         <v>51.1328248691887</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="79">
         <v>0</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="81">
         <v>52.6440266224902</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="83">
         <v>6.14386931075891</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="85">
         <v>31.2618646673367</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="87">
         <v>56.1438585749842</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="89">
         <v>17.9409319586569</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="91">
         <v>28.8537024098821</v>
       </c>
     </row>
@@ -8375,40 +8742,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="69">
         <v>29.4415234235124</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="71">
         <v>4.60823533281327</v>
       </c>
-      <c r="G8" s="58">
+      <c r="G8" s="73">
         <v>38.547238989568</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="75">
         <v>58.4990300690406</v>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="77">
         <v>48.3279628831578</v>
       </c>
-      <c r="J8" s="64">
+      <c r="J8" s="79">
         <v>0</v>
       </c>
-      <c r="K8" s="66">
+      <c r="K8" s="81">
         <v>56.9598859200096</v>
       </c>
-      <c r="L8" s="68">
+      <c r="L8" s="83">
         <v>1.3140510834644</v>
       </c>
-      <c r="M8" s="70">
+      <c r="M8" s="85">
         <v>28.999349021548</v>
       </c>
-      <c r="N8" s="72">
+      <c r="N8" s="87">
         <v>47.3521356910179</v>
       </c>
-      <c r="O8" s="74">
+      <c r="O8" s="89">
         <v>13.2706598771545</v>
       </c>
-      <c r="P8" s="76">
+      <c r="P8" s="91">
         <v>25.9782087908621</v>
       </c>
     </row>
@@ -8431,40 +8798,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="54">
+      <c r="E9" s="69">
         <v>26.5453289506458</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="71">
         <v>4.16820068206878</v>
       </c>
-      <c r="G9" s="58">
+      <c r="G9" s="73">
         <v>29.2181169146724</v>
       </c>
-      <c r="H9" s="60">
+      <c r="H9" s="75">
         <v>49.409585601462</v>
       </c>
-      <c r="I9" s="62">
+      <c r="I9" s="77">
         <v>48.158027028935</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="79">
         <v>0</v>
       </c>
-      <c r="K9" s="66">
+      <c r="K9" s="81">
         <v>45.0052820632008</v>
       </c>
-      <c r="L9" s="68">
+      <c r="L9" s="83">
         <v>0.334705622780934</v>
       </c>
-      <c r="M9" s="70">
+      <c r="M9" s="85">
         <v>51.3780743758556</v>
       </c>
-      <c r="N9" s="72">
+      <c r="N9" s="87">
         <v>41.2236627032475</v>
       </c>
-      <c r="O9" s="74">
+      <c r="O9" s="89">
         <v>14.4046371023227</v>
       </c>
-      <c r="P9" s="76">
+      <c r="P9" s="91">
         <v>8.69832636255856</v>
       </c>
     </row>
@@ -8487,40 +8854,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="54">
+      <c r="E10" s="69">
         <v>30.9497602480432</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="71">
         <v>6.14499246796124</v>
       </c>
-      <c r="G10" s="58">
+      <c r="G10" s="73">
         <v>40.3774970319426</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="75">
         <v>54.8222175293618</v>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="77">
         <v>47.8098452858986</v>
       </c>
-      <c r="J10" s="64">
+      <c r="J10" s="79">
         <v>0</v>
       </c>
-      <c r="K10" s="66">
+      <c r="K10" s="81">
         <v>47.7667856972464</v>
       </c>
-      <c r="L10" s="68">
+      <c r="L10" s="83">
         <v>4.15297684165933</v>
       </c>
-      <c r="M10" s="70">
+      <c r="M10" s="85">
         <v>51.1257187392647</v>
       </c>
-      <c r="N10" s="72">
+      <c r="N10" s="87">
         <v>46.9473150679871</v>
       </c>
-      <c r="O10" s="74">
+      <c r="O10" s="89">
         <v>18.4786731941389</v>
       </c>
-      <c r="P10" s="76">
+      <c r="P10" s="91">
         <v>22.8213408730139</v>
       </c>
     </row>
@@ -8543,40 +8910,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="54">
+      <c r="E11" s="69">
         <v>34.5411762516718</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="71">
         <v>8.73988866119368</v>
       </c>
-      <c r="G11" s="58">
+      <c r="G11" s="73">
         <v>39.779260433833</v>
       </c>
-      <c r="H11" s="60">
+      <c r="H11" s="75">
         <v>60.5397984222312</v>
       </c>
-      <c r="I11" s="62">
+      <c r="I11" s="77">
         <v>54.0559026870439</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="79">
         <v>0</v>
       </c>
-      <c r="K11" s="66">
+      <c r="K11" s="81">
         <v>52.6526787689207</v>
       </c>
-      <c r="L11" s="68">
+      <c r="L11" s="83">
         <v>10.0355807778393</v>
       </c>
-      <c r="M11" s="70">
+      <c r="M11" s="85">
         <v>50.9976686401245</v>
       </c>
-      <c r="N11" s="72">
+      <c r="N11" s="87">
         <v>54.9432355958725</v>
       </c>
-      <c r="O11" s="74">
+      <c r="O11" s="89">
         <v>24.2290514043257</v>
       </c>
-      <c r="P11" s="76">
+      <c r="P11" s="91">
         <v>23.979873377005</v>
       </c>
     </row>
@@ -8599,40 +8966,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="54">
+      <c r="E12" s="69">
         <v>30.8118202452212</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="71">
         <v>3.8343531874922</v>
       </c>
-      <c r="G12" s="58">
+      <c r="G12" s="73">
         <v>44.4758914394959</v>
       </c>
-      <c r="H12" s="60">
+      <c r="H12" s="75">
         <v>62.1440424633746</v>
       </c>
-      <c r="I12" s="62">
+      <c r="I12" s="77">
         <v>40.8573476997151</v>
       </c>
-      <c r="J12" s="64">
+      <c r="J12" s="79">
         <v>0</v>
       </c>
-      <c r="K12" s="66">
+      <c r="K12" s="81">
         <v>49.833851297815</v>
       </c>
-      <c r="L12" s="68">
+      <c r="L12" s="83">
         <v>5.95521189204785</v>
       </c>
-      <c r="M12" s="70">
+      <c r="M12" s="85">
         <v>27.4822579102775</v>
       </c>
-      <c r="N12" s="72">
+      <c r="N12" s="87">
         <v>48.9664560477312</v>
       </c>
-      <c r="O12" s="74">
+      <c r="O12" s="89">
         <v>33.252863153175</v>
       </c>
-      <c r="P12" s="76">
+      <c r="P12" s="91">
         <v>22.1277476063087</v>
       </c>
     </row>
@@ -8655,40 +9022,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="54">
+      <c r="E13" s="69">
         <v>27.2724679388026</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="71">
         <v>8.66363689457211</v>
       </c>
-      <c r="G13" s="58">
+      <c r="G13" s="73">
         <v>31.3040236468302</v>
       </c>
-      <c r="H13" s="60">
+      <c r="H13" s="75">
         <v>55.5397525048014</v>
       </c>
-      <c r="I13" s="62">
+      <c r="I13" s="77">
         <v>47.7724073962753</v>
       </c>
-      <c r="J13" s="64">
+      <c r="J13" s="79">
         <v>0</v>
       </c>
-      <c r="K13" s="66">
+      <c r="K13" s="81">
         <v>45.9496784203557</v>
       </c>
-      <c r="L13" s="68">
+      <c r="L13" s="83">
         <v>1.82047900810194</v>
       </c>
-      <c r="M13" s="70">
+      <c r="M13" s="85">
         <v>45.748084203262</v>
       </c>
-      <c r="N13" s="72">
+      <c r="N13" s="87">
         <v>36.1060406439479</v>
       </c>
-      <c r="O13" s="74">
+      <c r="O13" s="89">
         <v>12.310871572699</v>
       </c>
-      <c r="P13" s="76">
+      <c r="P13" s="91">
         <v>14.7821730359829</v>
       </c>
     </row>
@@ -8711,214 +9078,214 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="69">
         <v>35.0229514024448</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="71">
         <v>18.7536726643183</v>
       </c>
-      <c r="G14" s="58">
+      <c r="G14" s="73">
         <v>48.8714214567685</v>
       </c>
-      <c r="H14" s="60">
+      <c r="H14" s="75">
         <v>60.2893029474988</v>
       </c>
-      <c r="I14" s="62">
+      <c r="I14" s="77">
         <v>54.4337122200531</v>
       </c>
-      <c r="J14" s="64">
+      <c r="J14" s="79">
         <v>0</v>
       </c>
-      <c r="K14" s="66">
+      <c r="K14" s="81">
         <v>55.4360733084239</v>
       </c>
-      <c r="L14" s="68">
+      <c r="L14" s="83">
         <v>9.54977971601265</v>
       </c>
-      <c r="M14" s="70">
+      <c r="M14" s="85">
         <v>26.0188080739656</v>
       </c>
-      <c r="N14" s="72">
+      <c r="N14" s="87">
         <v>43.7548593664517</v>
       </c>
-      <c r="O14" s="74">
+      <c r="O14" s="89">
         <v>46.700805273895</v>
       </c>
-      <c r="P14" s="76">
+      <c r="P14" s="91">
         <v>21.4440303995047</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="68" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA (por población 2022)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="55">
+      <c r="C15" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="70">
         <v>30.3800620793865</v>
       </c>
-      <c r="F15" s="57">
+      <c r="F15" s="72">
         <v>8.92861182292848</v>
       </c>
-      <c r="G15" s="59">
+      <c r="G15" s="74">
         <v>37.1623672684875</v>
       </c>
-      <c r="H15" s="61">
+      <c r="H15" s="76">
         <v>55.5987827079859</v>
       </c>
-      <c r="I15" s="63">
+      <c r="I15" s="78">
         <v>49.4622045892582</v>
       </c>
-      <c r="J15" s="65">
+      <c r="J15" s="80">
         <v>0</v>
       </c>
-      <c r="K15" s="67">
+      <c r="K15" s="82">
         <v>50.262103707152</v>
       </c>
-      <c r="L15" s="69">
+      <c r="L15" s="84">
         <v>5.54533787649063</v>
       </c>
-      <c r="M15" s="71">
+      <c r="M15" s="86">
         <v>40.4904757811993</v>
       </c>
-      <c r="N15" s="73">
+      <c r="N15" s="88">
         <v>44.4945373577139</v>
       </c>
-      <c r="O15" s="75">
+      <c r="O15" s="90">
         <v>24.4968644671062</v>
       </c>
-      <c r="P15" s="77">
+      <c r="P15" s="92">
         <v>17.7393972949291</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B16" s="68" t="inlineStr">
         <is>
           <t>SUBREGIÓN NORTE (IMCA oficial de subregión)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E16" s="55">
+      <c r="C16" s="68" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D16" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E16" s="70">
         <v>32.4797103611666</v>
       </c>
-      <c r="F16" s="57">
+      <c r="F16" s="72">
         <v>9.28015207353694</v>
       </c>
-      <c r="G16" s="59">
+      <c r="G16" s="74">
         <v>41.9074122002197</v>
       </c>
-      <c r="H16" s="61">
+      <c r="H16" s="76">
         <v>58.4405416967164</v>
       </c>
-      <c r="I16" s="63">
+      <c r="I16" s="78">
         <v>50.6088657345118</v>
       </c>
-      <c r="J16" s="65">
+      <c r="J16" s="80">
         <v>0</v>
       </c>
-      <c r="K16" s="67">
+      <c r="K16" s="82">
         <v>52.6170318351737</v>
       </c>
-      <c r="L16" s="69">
+      <c r="L16" s="84">
         <v>8.22485538099614</v>
       </c>
-      <c r="M16" s="71">
+      <c r="M16" s="86">
         <v>43.6804795248635</v>
       </c>
-      <c r="N16" s="73">
+      <c r="N16" s="88">
         <v>47.6738144536003</v>
       </c>
-      <c r="O16" s="75">
+      <c r="O16" s="90">
         <v>23.3042940081032</v>
       </c>
-      <c r="P16" s="77">
+      <c r="P16" s="92">
         <v>21.5393670651105</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B17" s="68" t="inlineStr">
         <is>
           <t>SUBREGIÓN NORDESTE (IMCA oficial de subregión)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="68" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E17" s="55">
+      <c r="D17" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E17" s="70">
         <v>31.2784634829479</v>
       </c>
-      <c r="F17" s="57">
+      <c r="F17" s="72">
         <v>10.4976235197119</v>
       </c>
-      <c r="G17" s="59">
+      <c r="G17" s="74">
         <v>39.0177326208945</v>
       </c>
-      <c r="H17" s="61">
+      <c r="H17" s="76">
         <v>59.1892882445652</v>
       </c>
-      <c r="I17" s="63">
+      <c r="I17" s="78">
         <v>49.823101479487</v>
       </c>
-      <c r="J17" s="65">
+      <c r="J17" s="80">
         <v>0</v>
       </c>
-      <c r="K17" s="67">
+      <c r="K17" s="82">
         <v>48.1759834529013</v>
       </c>
-      <c r="L17" s="69">
+      <c r="L17" s="84">
         <v>10.7754315309344</v>
       </c>
-      <c r="M17" s="71">
+      <c r="M17" s="86">
         <v>44.307000298385</v>
       </c>
-      <c r="N17" s="73">
+      <c r="N17" s="88">
         <v>45.5791982610903</v>
       </c>
-      <c r="O17" s="75">
+      <c r="O17" s="90">
         <v>18.0008731890133</v>
       </c>
-      <c r="P17" s="77">
+      <c r="P17" s="92">
         <v>18.6968657154437</v>
       </c>
     </row>
@@ -8934,101 +9301,101 @@
   <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="86.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="87.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="94" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="94" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="94" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="94" t="inlineStr">
         <is>
           <t>Índice de Gobierno Digital</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="94" t="inlineStr">
         <is>
           <t>Gobernanza</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="94" t="inlineStr">
         <is>
           <t>Innovación Pública Digital</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="94" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="94" t="inlineStr">
         <is>
           <t>Seguridad y Privacidad de la Información</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="94" t="inlineStr">
         <is>
           <t>Servicios Ciudadanos Digitales</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="94" t="inlineStr">
         <is>
           <t>Cultura y Apropiación</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="94" t="inlineStr">
         <is>
           <t>Servicios y Procesos Inteligentes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="94" t="inlineStr">
         <is>
           <t>Estado Abierto</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="94" t="inlineStr">
         <is>
           <t>Decisiones basadas en datos</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="94" t="inlineStr">
         <is>
           <t>Proyectos de Transformación Digital</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="94" t="inlineStr">
         <is>
           <t>Estrategias de Ciudades y Territorios Inteligentes</t>
         </is>
@@ -9053,42 +9420,42 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="78">
+      <c r="E2" s="96">
         <v>53.85</v>
       </c>
-      <c r="F2" s="80">
+      <c r="F2" s="98">
         <v>50</v>
       </c>
-      <c r="G2" s="82">
+      <c r="G2" s="100">
         <v>0</v>
       </c>
-      <c r="H2" s="84">
+      <c r="H2" s="102">
         <v>16.67</v>
       </c>
-      <c r="I2" s="86">
+      <c r="I2" s="104">
         <v>25</v>
       </c>
-      <c r="J2" s="88">
+      <c r="J2" s="106">
         <v>0</v>
       </c>
-      <c r="K2" s="90">
+      <c r="K2" s="108">
         <v>0</v>
       </c>
-      <c r="L2" s="92">
+      <c r="L2" s="110">
         <v>22.22</v>
       </c>
-      <c r="M2" s="94">
+      <c r="M2" s="112">
         <v>81.33</v>
       </c>
-      <c r="N2" s="96">
+      <c r="N2" s="114">
         <v>12</v>
       </c>
-      <c r="O2" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" s="100" t="inlineStr">
+      <c r="O2" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9113,42 +9480,42 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="96">
         <v>41.97</v>
       </c>
-      <c r="F3" s="80">
+      <c r="F3" s="98">
         <v>50.08</v>
       </c>
-      <c r="G3" s="82">
+      <c r="G3" s="100">
         <v>25</v>
       </c>
-      <c r="H3" s="84">
+      <c r="H3" s="102">
         <v>16.67</v>
       </c>
-      <c r="I3" s="86">
+      <c r="I3" s="104">
         <v>33.33</v>
       </c>
-      <c r="J3" s="88">
+      <c r="J3" s="106">
         <v>44.33</v>
       </c>
-      <c r="K3" s="90">
+      <c r="K3" s="108">
         <v>0</v>
       </c>
-      <c r="L3" s="92">
+      <c r="L3" s="110">
         <v>19.44</v>
       </c>
-      <c r="M3" s="94">
+      <c r="M3" s="112">
         <v>53.33</v>
       </c>
-      <c r="N3" s="96">
+      <c r="N3" s="114">
         <v>31.03</v>
       </c>
-      <c r="O3" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" s="100" t="inlineStr">
+      <c r="O3" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9173,42 +9540,42 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="78">
+      <c r="E4" s="96">
         <v>52.36</v>
       </c>
-      <c r="F4" s="80">
+      <c r="F4" s="98">
         <v>58.42</v>
       </c>
-      <c r="G4" s="82">
+      <c r="G4" s="100">
         <v>0</v>
       </c>
-      <c r="H4" s="84">
+      <c r="H4" s="102">
         <v>60</v>
       </c>
-      <c r="I4" s="86">
+      <c r="I4" s="104">
         <v>31.82</v>
       </c>
-      <c r="J4" s="88">
+      <c r="J4" s="106">
         <v>25</v>
       </c>
-      <c r="K4" s="90">
+      <c r="K4" s="108">
         <v>0</v>
       </c>
-      <c r="L4" s="92">
+      <c r="L4" s="110">
         <v>13.89</v>
       </c>
-      <c r="M4" s="94">
+      <c r="M4" s="112">
         <v>62.8</v>
       </c>
-      <c r="N4" s="96">
+      <c r="N4" s="114">
         <v>0</v>
       </c>
-      <c r="O4" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" s="100" t="inlineStr">
+      <c r="O4" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9233,42 +9600,42 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="78">
+      <c r="E5" s="96">
         <v>68.78</v>
       </c>
-      <c r="F5" s="80">
+      <c r="F5" s="98">
         <v>63.94</v>
       </c>
-      <c r="G5" s="82">
+      <c r="G5" s="100">
         <v>0</v>
       </c>
-      <c r="H5" s="84">
+      <c r="H5" s="102">
         <v>44.44</v>
       </c>
-      <c r="I5" s="86">
+      <c r="I5" s="104">
         <v>79.46</v>
       </c>
-      <c r="J5" s="88">
+      <c r="J5" s="106">
         <v>75</v>
       </c>
-      <c r="K5" s="90">
+      <c r="K5" s="108">
         <v>100</v>
       </c>
-      <c r="L5" s="92">
+      <c r="L5" s="110">
         <v>0</v>
       </c>
-      <c r="M5" s="94">
+      <c r="M5" s="112">
         <v>79.27</v>
       </c>
-      <c r="N5" s="96">
+      <c r="N5" s="114">
         <v>75.86</v>
       </c>
-      <c r="O5" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" s="100" t="inlineStr">
+      <c r="O5" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9293,42 +9660,42 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="78">
+      <c r="E6" s="96">
         <v>64.36</v>
       </c>
-      <c r="F6" s="80">
+      <c r="F6" s="98">
         <v>50</v>
       </c>
-      <c r="G6" s="82">
+      <c r="G6" s="100">
         <v>45.75</v>
       </c>
-      <c r="H6" s="84">
+      <c r="H6" s="102">
         <v>22.22</v>
       </c>
-      <c r="I6" s="86">
+      <c r="I6" s="104">
         <v>0</v>
       </c>
-      <c r="J6" s="88">
+      <c r="J6" s="106">
         <v>0</v>
       </c>
-      <c r="K6" s="90">
+      <c r="K6" s="108">
         <v>48</v>
       </c>
-      <c r="L6" s="92">
+      <c r="L6" s="110">
         <v>37.5</v>
       </c>
-      <c r="M6" s="94">
+      <c r="M6" s="112">
         <v>94.67</v>
       </c>
-      <c r="N6" s="96">
+      <c r="N6" s="114">
         <v>0</v>
       </c>
-      <c r="O6" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" s="100" t="inlineStr">
+      <c r="O6" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9353,40 +9720,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="78">
+      <c r="E7" s="96">
         <v>89.36</v>
       </c>
-      <c r="F7" s="80">
+      <c r="F7" s="98">
         <v>83.33</v>
       </c>
-      <c r="G7" s="82">
+      <c r="G7" s="100">
         <v>100</v>
       </c>
-      <c r="H7" s="84">
+      <c r="H7" s="102">
         <v>69.44</v>
       </c>
-      <c r="I7" s="86">
+      <c r="I7" s="104">
         <v>88.07</v>
       </c>
-      <c r="J7" s="88">
+      <c r="J7" s="106">
         <v>100</v>
       </c>
-      <c r="K7" s="90">
+      <c r="K7" s="108">
         <v>100</v>
       </c>
-      <c r="L7" s="92">
+      <c r="L7" s="110">
         <v>22.22</v>
       </c>
-      <c r="M7" s="94">
+      <c r="M7" s="112">
         <v>97.56</v>
       </c>
-      <c r="N7" s="96">
+      <c r="N7" s="114">
         <v>96.55</v>
       </c>
-      <c r="O7" s="98">
+      <c r="O7" s="116">
         <v>100</v>
       </c>
-      <c r="P7" s="100">
+      <c r="P7" s="118">
         <v>100</v>
       </c>
     </row>
@@ -9409,42 +9776,42 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="78">
+      <c r="E8" s="96">
         <v>64.84</v>
       </c>
-      <c r="F8" s="80">
+      <c r="F8" s="98">
         <v>76.39</v>
       </c>
-      <c r="G8" s="82">
+      <c r="G8" s="100">
         <v>0</v>
       </c>
-      <c r="H8" s="84">
+      <c r="H8" s="102">
         <v>28.89</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="104">
         <v>44.42</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="106">
         <v>0</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="108">
         <v>100</v>
       </c>
-      <c r="L8" s="92">
+      <c r="L8" s="110">
         <v>22.22</v>
       </c>
-      <c r="M8" s="94">
+      <c r="M8" s="112">
         <v>87.2</v>
       </c>
-      <c r="N8" s="96">
+      <c r="N8" s="114">
         <v>36</v>
       </c>
-      <c r="O8" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P8" s="100" t="inlineStr">
+      <c r="O8" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9469,42 +9836,42 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="78">
+      <c r="E9" s="96">
         <v>63.34</v>
       </c>
-      <c r="F9" s="80">
+      <c r="F9" s="98">
         <v>74.94</v>
       </c>
-      <c r="G9" s="82">
+      <c r="G9" s="100">
         <v>0</v>
       </c>
-      <c r="H9" s="84">
+      <c r="H9" s="102">
         <v>0</v>
       </c>
-      <c r="I9" s="86">
+      <c r="I9" s="104">
         <v>75.67</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="106">
         <v>33.33</v>
       </c>
-      <c r="K9" s="90">
+      <c r="K9" s="108">
         <v>76</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="110">
         <v>55.56</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="112">
         <v>81.71</v>
       </c>
-      <c r="N9" s="96">
+      <c r="N9" s="114">
         <v>16</v>
       </c>
-      <c r="O9" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P9" s="100" t="inlineStr">
+      <c r="O9" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9529,42 +9896,42 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="78">
+      <c r="E10" s="96">
         <v>11.65</v>
       </c>
-      <c r="F10" s="80">
+      <c r="F10" s="98">
         <v>37.58</v>
       </c>
-      <c r="G10" s="82">
+      <c r="G10" s="100">
         <v>0</v>
       </c>
-      <c r="H10" s="84">
+      <c r="H10" s="102">
         <v>16.67</v>
       </c>
-      <c r="I10" s="86">
+      <c r="I10" s="104">
         <v>10</v>
       </c>
-      <c r="J10" s="88">
+      <c r="J10" s="106">
         <v>0</v>
       </c>
-      <c r="K10" s="90">
+      <c r="K10" s="108">
         <v>0</v>
       </c>
-      <c r="L10" s="92">
+      <c r="L10" s="110">
         <v>0</v>
       </c>
-      <c r="M10" s="94">
+      <c r="M10" s="112">
         <v>12</v>
       </c>
-      <c r="N10" s="96">
+      <c r="N10" s="114">
         <v>0</v>
       </c>
-      <c r="O10" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P10" s="100" t="inlineStr">
+      <c r="O10" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9589,42 +9956,42 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="78">
+      <c r="E11" s="96">
         <v>62.34</v>
       </c>
-      <c r="F11" s="80">
+      <c r="F11" s="98">
         <v>50.06</v>
       </c>
-      <c r="G11" s="82">
+      <c r="G11" s="100">
         <v>0</v>
       </c>
-      <c r="H11" s="84">
+      <c r="H11" s="102">
         <v>16.67</v>
       </c>
-      <c r="I11" s="86">
+      <c r="I11" s="104">
         <v>25</v>
       </c>
-      <c r="J11" s="88">
+      <c r="J11" s="106">
         <v>0</v>
       </c>
-      <c r="K11" s="90">
+      <c r="K11" s="108">
         <v>68</v>
       </c>
-      <c r="L11" s="92">
+      <c r="L11" s="110">
         <v>11.11</v>
       </c>
-      <c r="M11" s="94">
+      <c r="M11" s="112">
         <v>76</v>
       </c>
-      <c r="N11" s="96">
+      <c r="N11" s="114">
         <v>65.52</v>
       </c>
-      <c r="O11" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P11" s="100" t="inlineStr">
+      <c r="O11" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9649,40 +10016,40 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="78">
+      <c r="E12" s="96">
         <v>72.44</v>
       </c>
-      <c r="F12" s="80">
+      <c r="F12" s="98">
         <v>80.56</v>
       </c>
-      <c r="G12" s="82">
+      <c r="G12" s="100">
         <v>69.33</v>
       </c>
-      <c r="H12" s="84">
+      <c r="H12" s="102">
         <v>15.56</v>
       </c>
-      <c r="I12" s="86">
+      <c r="I12" s="104">
         <v>25</v>
       </c>
-      <c r="J12" s="88">
+      <c r="J12" s="106">
         <v>44.33</v>
       </c>
-      <c r="K12" s="90">
+      <c r="K12" s="108">
         <v>0</v>
       </c>
-      <c r="L12" s="92">
+      <c r="L12" s="110">
         <v>30.56</v>
       </c>
-      <c r="M12" s="94">
+      <c r="M12" s="112">
         <v>95.73</v>
       </c>
-      <c r="N12" s="96">
+      <c r="N12" s="114">
         <v>62.07</v>
       </c>
-      <c r="O12" s="98">
+      <c r="O12" s="116">
         <v>100</v>
       </c>
-      <c r="P12" s="100" t="inlineStr">
+      <c r="P12" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9707,218 +10074,218 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="78">
+      <c r="E13" s="96">
         <v>52.21</v>
       </c>
-      <c r="F13" s="80">
+      <c r="F13" s="98">
         <v>50.08</v>
       </c>
-      <c r="G13" s="82">
+      <c r="G13" s="100">
         <v>0</v>
       </c>
-      <c r="H13" s="84">
+      <c r="H13" s="102">
         <v>40</v>
       </c>
-      <c r="I13" s="86">
+      <c r="I13" s="104">
         <v>6.6</v>
       </c>
-      <c r="J13" s="88">
+      <c r="J13" s="106">
         <v>0</v>
       </c>
-      <c r="K13" s="90">
+      <c r="K13" s="108">
         <v>0</v>
       </c>
-      <c r="L13" s="92">
+      <c r="L13" s="110">
         <v>16.67</v>
       </c>
-      <c r="M13" s="94">
+      <c r="M13" s="112">
         <v>79.27</v>
       </c>
-      <c r="N13" s="96">
+      <c r="N13" s="114">
         <v>13.79</v>
       </c>
-      <c r="O13" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P13" s="100" t="inlineStr">
+      <c r="O13" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA (por población 2024)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E14" s="79">
+      <c r="C14" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="97">
         <v>57.7067997362189</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="99">
         <v>60.3269740115704</v>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="101">
         <v>16.0955247744372</v>
       </c>
-      <c r="H14" s="85">
+      <c r="H14" s="103">
         <v>29.6080399268607</v>
       </c>
-      <c r="I14" s="87">
+      <c r="I14" s="105">
         <v>29.2146026797758</v>
       </c>
-      <c r="J14" s="89">
+      <c r="J14" s="107">
         <v>18.0202043104224</v>
       </c>
-      <c r="K14" s="91">
+      <c r="K14" s="109">
         <v>32.648709571056</v>
       </c>
-      <c r="L14" s="93">
+      <c r="L14" s="111">
         <v>21.7696658973052</v>
       </c>
-      <c r="M14" s="95">
+      <c r="M14" s="113">
         <v>78.4961326099338</v>
       </c>
-      <c r="N14" s="97">
+      <c r="N14" s="115">
         <v>28.673581607266</v>
       </c>
-      <c r="O14" s="99">
+      <c r="O14" s="117">
         <v>100</v>
       </c>
-      <c r="P14" s="101">
+      <c r="P14" s="119">
         <v>100</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN NORTE (por población 2024)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="79">
+      <c r="C15" s="95" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D15" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="97">
         <v>62.1143595323915</v>
       </c>
-      <c r="F15" s="81">
+      <c r="F15" s="99">
         <v>60.679905786374</v>
       </c>
-      <c r="G15" s="83">
+      <c r="G15" s="101">
         <v>23.2966390435426</v>
       </c>
-      <c r="H15" s="85">
+      <c r="H15" s="103">
         <v>33.8909365445885</v>
       </c>
-      <c r="I15" s="87">
+      <c r="I15" s="105">
         <v>48.5757102227014</v>
       </c>
-      <c r="J15" s="89">
+      <c r="J15" s="107">
         <v>17.6279142261771</v>
       </c>
-      <c r="K15" s="91">
+      <c r="K15" s="109">
         <v>44.0155392141087</v>
       </c>
-      <c r="L15" s="93">
+      <c r="L15" s="111">
         <v>19.998202257587</v>
       </c>
-      <c r="M15" s="95">
+      <c r="M15" s="113">
         <v>83.1339263991246</v>
       </c>
-      <c r="N15" s="97">
+      <c r="N15" s="115">
         <v>25.7734276944614</v>
       </c>
-      <c r="O15" s="99">
+      <c r="O15" s="117">
         <v>79.3092310976695</v>
       </c>
-      <c r="P15" s="101">
+      <c r="P15" s="119">
         <v>61.4050885752644</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B16" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN NORDESTE (por población 2024)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="95" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E16" s="79">
+      <c r="D16" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E16" s="97">
         <v>61.1200864444942</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="99">
         <v>61.3074069983863</v>
       </c>
-      <c r="G16" s="83">
+      <c r="G16" s="101">
         <v>26.1217137525764</v>
       </c>
-      <c r="H16" s="85">
+      <c r="H16" s="103">
         <v>27.0592596048116</v>
       </c>
-      <c r="I16" s="87">
+      <c r="I16" s="105">
         <v>41.8230762053914</v>
       </c>
-      <c r="J16" s="89">
+      <c r="J16" s="107">
         <v>5.70210089633801</v>
       </c>
-      <c r="K16" s="91">
+      <c r="K16" s="109">
         <v>51.5553542748611</v>
       </c>
-      <c r="L16" s="93">
+      <c r="L16" s="111">
         <v>14.060984020145</v>
       </c>
-      <c r="M16" s="95">
+      <c r="M16" s="113">
         <v>80.2975782689204</v>
       </c>
-      <c r="N16" s="97">
+      <c r="N16" s="115">
         <v>25.262751134108</v>
       </c>
-      <c r="O16" s="99">
+      <c r="O16" s="117">
         <v>20.0420134364821</v>
       </c>
-      <c r="P16" s="101" t="inlineStr">
+      <c r="P16" s="119" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9936,35 +10303,35 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="62.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="63.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="121" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="121" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="121" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="121" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="121" t="inlineStr">
         <is>
           <t>Tasa de tránsito inmediato a la educación superior</t>
         </is>
@@ -9989,7 +10356,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="102">
+      <c r="E2" s="123">
         <v>0.138888888888889</v>
       </c>
     </row>
@@ -10012,7 +10379,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="102">
+      <c r="E3" s="123">
         <v>0.203592814371257</v>
       </c>
     </row>
@@ -10035,7 +10402,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="102">
+      <c r="E4" s="123">
         <v>0.384615384615385</v>
       </c>
     </row>
@@ -10058,7 +10425,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="123">
         <v>0.153846153846154</v>
       </c>
     </row>
@@ -10081,7 +10448,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="102">
+      <c r="E6" s="123">
         <v>0.473684210526316</v>
       </c>
     </row>
@@ -10104,7 +10471,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="102">
+      <c r="E7" s="123">
         <v>0.544303797468354</v>
       </c>
     </row>
@@ -10127,7 +10494,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="102">
+      <c r="E8" s="123">
         <v>0.489795918367347</v>
       </c>
     </row>
@@ -10150,7 +10517,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="102">
+      <c r="E9" s="123">
         <v>0.214611872146119</v>
       </c>
     </row>
@@ -10173,7 +10540,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="102">
+      <c r="E10" s="123">
         <v>0.447761194029851</v>
       </c>
     </row>
@@ -10196,7 +10563,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="102">
+      <c r="E11" s="123">
         <v>0.176470588235294</v>
       </c>
     </row>
@@ -10219,7 +10586,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="102">
+      <c r="E12" s="123">
         <v>0.372093023255814</v>
       </c>
     </row>
@@ -10242,7 +10609,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="102">
+      <c r="E13" s="123">
         <v>0.277777777777778</v>
       </c>
     </row>
@@ -10265,32 +10632,32 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="102">
+      <c r="E14" s="123">
         <v>0.272357723577236</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="122" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="103">
+      <c r="C15" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="124">
         <v>0.319215334392753</v>
       </c>
     </row>
@@ -10306,53 +10673,53 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="62.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="58.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="102.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="126" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="126" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="126" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="126" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por fibra óptica</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="126" t="inlineStr">
         <is>
           <t>Proporción de líneas sobre fibra óptica</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por cada 1.000 habitantes</t>
         </is>
@@ -10377,17 +10744,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="104">
-        <v>1365</v>
-      </c>
-      <c r="F2" s="106">
-        <v>462</v>
-      </c>
-      <c r="G2" s="108">
-        <v>0.338461538461538</v>
-      </c>
-      <c r="H2" s="110">
-        <v>109.103988490129</v>
+      <c r="E2" s="128">
+        <v>573</v>
+      </c>
+      <c r="F2" s="130">
+        <v>319</v>
+      </c>
+      <c r="G2" s="132">
+        <v>0.556719022687609</v>
+      </c>
+      <c r="H2" s="134">
+        <v>45.7996962672848</v>
       </c>
     </row>
     <row r="3">
@@ -10409,17 +10776,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="104">
-        <v>9780</v>
-      </c>
-      <c r="F3" s="106">
-        <v>6315</v>
-      </c>
-      <c r="G3" s="108">
-        <v>0.645705521472393</v>
-      </c>
-      <c r="H3" s="110">
-        <v>464.939386736392</v>
+      <c r="E3" s="128">
+        <v>2848</v>
+      </c>
+      <c r="F3" s="130">
+        <v>1825</v>
+      </c>
+      <c r="G3" s="132">
+        <v>0.640800561797753</v>
+      </c>
+      <c r="H3" s="134">
+        <v>135.393391965771</v>
       </c>
     </row>
     <row r="4">
@@ -10441,17 +10808,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="104">
-        <v>2492</v>
-      </c>
-      <c r="F4" s="106">
-        <v>52</v>
-      </c>
-      <c r="G4" s="108">
-        <v>0.0208667736757624</v>
-      </c>
-      <c r="H4" s="110">
-        <v>313.183360563026</v>
+      <c r="E4" s="128">
+        <v>633</v>
+      </c>
+      <c r="F4" s="130">
+        <v>14</v>
+      </c>
+      <c r="G4" s="132">
+        <v>0.0221169036334913</v>
+      </c>
+      <c r="H4" s="134">
+        <v>79.5525951991957</v>
       </c>
     </row>
     <row r="5">
@@ -10473,17 +10840,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="104">
-        <v>2190</v>
-      </c>
-      <c r="F5" s="106">
-        <v>1719</v>
-      </c>
-      <c r="G5" s="108">
-        <v>0.784931506849315</v>
-      </c>
-      <c r="H5" s="110">
-        <v>218.890554722639</v>
+      <c r="E5" s="128">
+        <v>786</v>
+      </c>
+      <c r="F5" s="130">
+        <v>616</v>
+      </c>
+      <c r="G5" s="132">
+        <v>0.783715012722646</v>
+      </c>
+      <c r="H5" s="134">
+        <v>78.5607196401799</v>
       </c>
     </row>
     <row r="6">
@@ -10505,17 +10872,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="104">
-        <v>2227</v>
-      </c>
-      <c r="F6" s="106">
-        <v>1941</v>
-      </c>
-      <c r="G6" s="108">
-        <v>0.871576111360575</v>
-      </c>
-      <c r="H6" s="110">
-        <v>564.94165398275</v>
+      <c r="E6" s="128">
+        <v>553</v>
+      </c>
+      <c r="F6" s="130">
+        <v>439</v>
+      </c>
+      <c r="G6" s="132">
+        <v>0.793851717902351</v>
+      </c>
+      <c r="H6" s="134">
+        <v>140.284119736175</v>
       </c>
     </row>
     <row r="7">
@@ -10537,17 +10904,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="104">
-        <v>4882</v>
-      </c>
-      <c r="F7" s="106">
-        <v>4250</v>
-      </c>
-      <c r="G7" s="108">
-        <v>0.870544858664482</v>
-      </c>
-      <c r="H7" s="110">
-        <v>470.644943603586</v>
+      <c r="E7" s="128">
+        <v>1161</v>
+      </c>
+      <c r="F7" s="130">
+        <v>914</v>
+      </c>
+      <c r="G7" s="132">
+        <v>0.787252368647718</v>
+      </c>
+      <c r="H7" s="134">
+        <v>111.925190398149</v>
       </c>
     </row>
     <row r="8">
@@ -10569,17 +10936,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="104">
-        <v>1430</v>
-      </c>
-      <c r="F8" s="106">
-        <v>723</v>
-      </c>
-      <c r="G8" s="108">
-        <v>0.505594405594406</v>
-      </c>
-      <c r="H8" s="110">
-        <v>204.023398487659</v>
+      <c r="E8" s="128">
+        <v>510</v>
+      </c>
+      <c r="F8" s="130">
+        <v>277</v>
+      </c>
+      <c r="G8" s="132">
+        <v>0.543137254901961</v>
+      </c>
+      <c r="H8" s="134">
+        <v>72.7635896704237</v>
       </c>
     </row>
     <row r="9">
@@ -10601,17 +10968,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="104">
-        <v>1810</v>
-      </c>
-      <c r="F9" s="106">
-        <v>147</v>
-      </c>
-      <c r="G9" s="108">
-        <v>0.0812154696132597</v>
-      </c>
-      <c r="H9" s="110">
-        <v>61.324750127054</v>
+      <c r="E9" s="128">
+        <v>547</v>
+      </c>
+      <c r="F9" s="130">
+        <v>4</v>
+      </c>
+      <c r="G9" s="132">
+        <v>0.00731261425959781</v>
+      </c>
+      <c r="H9" s="134">
+        <v>18.5329493477893</v>
       </c>
     </row>
     <row r="10">
@@ -10633,17 +11000,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="104">
-        <v>1580</v>
-      </c>
-      <c r="F10" s="106">
-        <v>1322</v>
-      </c>
-      <c r="G10" s="108">
-        <v>0.836708860759494</v>
-      </c>
-      <c r="H10" s="110">
-        <v>213.455822750608</v>
+      <c r="E10" s="128">
+        <v>421</v>
+      </c>
+      <c r="F10" s="130">
+        <v>330</v>
+      </c>
+      <c r="G10" s="132">
+        <v>0.783847980997625</v>
+      </c>
+      <c r="H10" s="134">
+        <v>56.8765198594974</v>
       </c>
     </row>
     <row r="11">
@@ -10665,17 +11032,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="104">
-        <v>637</v>
-      </c>
-      <c r="F11" s="106">
-        <v>383</v>
-      </c>
-      <c r="G11" s="108">
-        <v>0.601255886970173</v>
-      </c>
-      <c r="H11" s="110">
-        <v>158.576051779935</v>
+      <c r="E11" s="128">
+        <v>96</v>
+      </c>
+      <c r="F11" s="130">
+        <v>2</v>
+      </c>
+      <c r="G11" s="132">
+        <v>0.0208333333333333</v>
+      </c>
+      <c r="H11" s="134">
+        <v>23.898431665422</v>
       </c>
     </row>
     <row r="12">
@@ -10697,17 +11064,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="104">
-        <v>585</v>
-      </c>
-      <c r="F12" s="106">
-        <v>101</v>
-      </c>
-      <c r="G12" s="108">
-        <v>0.172649572649573</v>
-      </c>
-      <c r="H12" s="110">
-        <v>121.268656716418</v>
+      <c r="E12" s="128">
+        <v>184</v>
+      </c>
+      <c r="F12" s="130">
+        <v>2</v>
+      </c>
+      <c r="G12" s="132">
+        <v>0.0108695652173913</v>
+      </c>
+      <c r="H12" s="134">
+        <v>38.1426202321725</v>
       </c>
     </row>
     <row r="13">
@@ -10729,17 +11096,17 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="104">
-        <v>3478</v>
-      </c>
-      <c r="F13" s="106">
-        <v>715</v>
-      </c>
-      <c r="G13" s="108">
-        <v>0.205577918343876</v>
-      </c>
-      <c r="H13" s="110">
-        <v>231.650459571067</v>
+      <c r="E13" s="128">
+        <v>935</v>
+      </c>
+      <c r="F13" s="130">
+        <v>281</v>
+      </c>
+      <c r="G13" s="132">
+        <v>0.300534759358289</v>
+      </c>
+      <c r="H13" s="134">
+        <v>62.2752098041828</v>
       </c>
     </row>
     <row r="14">
@@ -10761,51 +11128,51 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="104">
-        <v>18100</v>
-      </c>
-      <c r="F14" s="106">
-        <v>15784</v>
-      </c>
-      <c r="G14" s="108">
-        <v>0.872044198895028</v>
-      </c>
-      <c r="H14" s="110">
-        <v>432.145926845574</v>
+      <c r="E14" s="128">
+        <v>5450</v>
+      </c>
+      <c r="F14" s="130">
+        <v>4780</v>
+      </c>
+      <c r="G14" s="132">
+        <v>0.877064220183486</v>
+      </c>
+      <c r="H14" s="134">
+        <v>130.121287365104</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO SIMPLE PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="105">
-        <v>3888.92307692308</v>
-      </c>
-      <c r="F15" s="107">
-        <v>2608.76923076923</v>
-      </c>
-      <c r="G15" s="109">
-        <v>0.523625586408452</v>
-      </c>
-      <c r="H15" s="111">
-        <v>274.165304182833</v>
+      <c r="A15" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="127" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA (suma de líneas; razones recalculadas sobre las sumas)</t>
+        </is>
+      </c>
+      <c r="C15" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="129">
+        <v>14697</v>
+      </c>
+      <c r="F15" s="131">
+        <v>9803</v>
+      </c>
+      <c r="G15" s="133">
+        <v>0.667006872150779</v>
+      </c>
+      <c r="H15" s="135">
+        <v>83.7493161925602</v>
       </c>
     </row>
   </sheetData>
